--- a/data/margen_operativo.xlsx
+++ b/data/margen_operativo.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>309357831.94</v>
+        <v>859094388.4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>309357831.94</v>
+        <v>859094388.4</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -524,7 +524,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>295397983.16</v>
+        <v>397069087.04</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>295397983.16</v>
+        <v>397069087.04</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -562,7 +562,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>310460436.03</v>
+        <v>412964886.94</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>310460436.03</v>
+        <v>412964886.94</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -600,7 +600,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>319457770.66</v>
+        <v>384295845.86</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>319457770.66</v>
+        <v>384295845.86</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -638,7 +638,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>283740248</v>
+        <v>659110187.95</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>283740248</v>
+        <v>659110187.95</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>281725231.9</v>
+        <v>309357831.94</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>281725231.9</v>
+        <v>309357831.94</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -714,7 +714,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>307205552.92</v>
+        <v>316737753.4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>307205552.92</v>
+        <v>316737753.4</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -752,7 +752,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>289159479.7</v>
+        <v>295397983.16</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>289159479.7</v>
+        <v>295397983.16</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -790,7 +790,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>316737753.4</v>
+        <v>310460436.03</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>316737753.4</v>
+        <v>310460436.03</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -823,43 +823,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bsas Cargas Sociales</t>
+          <t>Ventas netas - Salta</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8067993.66</v>
+        <v>319457770.66</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>42101009</t>
+          <t xml:space="preserve">     </t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>-8067993.66</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>ASIENTO SUELDOS ENERO 2025</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>31/01/2025</t>
-        </is>
-      </c>
+        <v>319457770.66</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>PERSONAL</t>
+          <t>1.VENTAS</t>
         </is>
       </c>
     </row>
@@ -869,43 +861,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Bsas Cargas Sociales</t>
+          <t>Ventas netas - Salta</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2509915.43</v>
+        <v>283740248</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>42102005</t>
+          <t xml:space="preserve">     </t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>-2509915.43</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SUELDOS MAYO </t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>31/05/2025</t>
-        </is>
-      </c>
+        <v>283740248</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>PERSONAL</t>
+          <t>1.VENTAS</t>
         </is>
       </c>
     </row>
@@ -915,43 +899,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Bsas Cargas Sociales</t>
+          <t>Ventas netas - Salta</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>12693514.15</v>
+        <v>281725231.9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>42101009</t>
+          <t xml:space="preserve">     </t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>-12693514.15</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SUELDOS MAYO </t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>31/05/2025</t>
-        </is>
-      </c>
+        <v>281725231.9</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>PERSONAL</t>
+          <t>1.VENTAS</t>
         </is>
       </c>
     </row>
@@ -961,7 +937,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -971,33 +947,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Bsas Cargas Sociales</t>
+          <t>Ventas netas - Salta</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>7745265.19</v>
+        <v>307205552.92</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>42101009</t>
+          <t xml:space="preserve">     </t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>-7745265.19</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>ASIENTO SUELDOS FEBRERO 2025</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>28/02/2025</t>
-        </is>
-      </c>
+        <v>307205552.92</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>PERSONAL</t>
+          <t>1.VENTAS</t>
         </is>
       </c>
     </row>
@@ -1007,43 +975,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bsas Cargas Sociales</t>
+          <t>Ventas netas - Salta</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1895120.93</v>
+        <v>289159479.7</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>42102005</t>
+          <t xml:space="preserve">     </t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>-1895120.93</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>ASIENTO SUELDOS FEBRERO 2025</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>28/02/2025</t>
-        </is>
-      </c>
+        <v>289159479.7</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>PERSONAL</t>
+          <t>1.VENTAS</t>
         </is>
       </c>
     </row>
@@ -1053,43 +1013,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bsas Cargas Sociales</t>
+          <t>Ventas netas - Salta</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2258902.99</v>
+        <v>365136068.36</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>42102005</t>
+          <t xml:space="preserve">     </t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>-2258902.99</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>ASTO SUELDOS ABRIL 2025</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>30/04/2025</t>
-        </is>
-      </c>
+        <v>365136068.36</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>PERSONAL</t>
+          <t>1.VENTAS</t>
         </is>
       </c>
     </row>
@@ -1099,43 +1051,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bsas Cargas Sociales</t>
+          <t>Ventas netas - Salta</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>10116157.5</v>
+        <v>399461069</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>42101009</t>
+          <t xml:space="preserve">     </t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>-10116157.5</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>ASTO SUELDOS ABRIL 2025</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>30/04/2025</t>
-        </is>
-      </c>
+        <v>399461069</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>PERSONAL</t>
+          <t>1.VENTAS</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1094,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1159,24 +1103,24 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2613068.89</v>
+        <v>8067993.66</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>42102005</t>
+          <t>42101009</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>-2613068.89</v>
+        <v>-8067993.66</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Prov Agosto 25</t>
+          <t>ASIENTO SUELDOS ENERO 2025</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>31/08/2025</t>
+          <t>31/01/2025</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1288,7 +1232,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1297,24 +1241,24 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1848813.12</v>
+        <v>11884681.73</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>42102005</t>
+          <t>42101009</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>-1848813.12</v>
+        <v>-11884681.73</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>ASTO SUELDOS MARZO 2025</t>
+          <t>Prov Agosto 25</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>31/03/2025</t>
+          <t>31/08/2025</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1334,7 +1278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1343,24 +1287,24 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>7928957.94</v>
+        <v>2471655.07</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>42101009</t>
+          <t>42102005</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>-7928957.94</v>
+        <v>-2471655.07</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>ASTO SUELDOS MARZO 2025</t>
+          <t>ASIENTO DE SUELDOS AGOSTO 25</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>31/03/2025</t>
+          <t>31/08/2025</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1380,7 +1324,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1389,24 +1333,24 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2495704.88</v>
+        <v>7745265.19</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>42102005</t>
+          <t>42101009</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>-2495704.88</v>
+        <v>-7745265.19</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>SUELDOS JUNIO 2025</t>
+          <t>ASIENTO SUELDOS FEBRERO 2025</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>30/06/2025</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1426,7 +1370,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1435,24 +1379,24 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>11884681.73</v>
+        <v>1895120.93</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>42101009</t>
+          <t>42102005</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>-11884681.73</v>
+        <v>-1895120.93</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Prov Agosto 25</t>
+          <t>ASIENTO SUELDOS FEBRERO 2025</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>31/08/2025</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1472,7 +1416,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1481,24 +1425,24 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>19701.98</v>
+        <v>2509915.43</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>42101009</t>
+          <t>42102005</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>-19701.98</v>
+        <v>-2509915.43</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>ASTO RECLASIF Y CONC DE CTAS</t>
+          <t xml:space="preserve">SUELDOS MAYO </t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>30/06/2025</t>
+          <t>31/05/2025</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1518,7 +1462,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1527,7 +1471,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>11449872.27</v>
+        <v>12693514.15</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1535,16 +1479,16 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>-11449872.27</v>
+        <v>-12693514.15</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>ASIENTO SUELDOS JULIO 25</t>
+          <t xml:space="preserve">SUELDOS MAYO </t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>31/07/2025</t>
+          <t>31/05/2025</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1564,7 +1508,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1573,7 +1517,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>97407.75</v>
+        <v>7928957.94</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1581,16 +1525,16 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>-97407.75</v>
+        <v>-7928957.94</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Comprobante - OSECAC - 46157</t>
+          <t>ASTO SUELDOS MARZO 2025</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>29/04/2025</t>
+          <t>31/03/2025</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1610,7 +1554,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1619,7 +1563,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4153633.35</v>
+        <v>1848813.12</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1627,16 +1571,16 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>-4153633.35</v>
+        <v>-1848813.12</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>ASIENTO SUELDOS JULIO 25</t>
+          <t>ASTO SUELDOS MARZO 2025</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>31/07/2025</t>
+          <t>31/03/2025</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1656,33 +1600,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Bsas Sueldos</t>
+          <t>Bsas Cargas Sociales</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>40195172.43</v>
+        <v>97407.75</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>42101029</t>
+          <t>42101009</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>-40195172.43</v>
+        <v>-97407.75</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Prov Agosto 25</t>
+          <t>Comprobante - OSECAC - 46157</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>31/08/2025</t>
+          <t>29/04/2025</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1702,33 +1646,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Bsas Sueldos</t>
+          <t>Bsas Cargas Sociales</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>38826779.14</v>
+        <v>2626293.25</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>42101029</t>
+          <t>42102005</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>-38826779.14</v>
+        <v>-2626293.25</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>ASTO SUELDOS ABRIL 2025</t>
+          <t>ASIENTO DE SUELDOS SEPTIEMBRE</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>30/04/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1748,33 +1692,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Bsas Sueldos</t>
+          <t>Bsas Cargas Sociales</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>16822069.17</v>
+        <v>11577991.95</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>42102023</t>
+          <t>42101009</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>-16822069.17</v>
+        <v>-11577991.95</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>ASIENTO SUELDOS JULIO 25</t>
+          <t>ASIENTO DE SUELDOS SEPTIEMBRE</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>31/07/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1794,33 +1738,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Bsas Sueldos</t>
+          <t>Bsas Cargas Sociales</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>8834638.699999999</v>
+        <v>2873305.09</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>42102023</t>
+          <t>42102005</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>-8834638.699999999</v>
+        <v>-2873305.09</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>ASTO SUELDOS ABRIL 2025</t>
+          <t>ASIENTO DE SUELDOS OCTUBRE 25</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>30/04/2025</t>
+          <t>31/10/2025</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1840,33 +1784,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Bsas Sueldos</t>
+          <t>Bsas Cargas Sociales</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>43537788.49</v>
+        <v>2495704.88</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>42101029</t>
+          <t>42102005</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>-43537788.49</v>
+        <v>-2495704.88</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>ASIENTO SUELDOS JULIO 25</t>
+          <t>SUELDOS JUNIO 2025</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>31/07/2025</t>
+          <t>30/06/2025</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1886,33 +1830,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Bsas Sueldos</t>
+          <t>Bsas Cargas Sociales</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>13413532.38</v>
+        <v>12643342.42</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>42102023</t>
+          <t>42101009</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>-13413532.38</v>
+        <v>-12643342.42</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SUELDOS JUNIO 2025</t>
+          <t>ASIENTO DE SUELDOS OCTUBRE 25</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>30/06/2025</t>
+          <t>31/10/2025</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -1932,33 +1876,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Bsas Sueldos</t>
+          <t>Bsas Cargas Sociales</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>9272920.189999999</v>
+        <v>2258902.99</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>42102023</t>
+          <t>42102005</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>-9272920.189999999</v>
+        <v>-2258902.99</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUELDOS MAYO </t>
+          <t>ASTO SUELDOS ABRIL 2025</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>31/05/2025</t>
+          <t>30/04/2025</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -1978,33 +1922,33 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Bsas Sueldos</t>
+          <t>Bsas Cargas Sociales</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>143074383.93</v>
+        <v>10691359.21</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>42101029</t>
+          <t>42101009</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>-143074383.93</v>
+        <v>-10691359.21</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SUELDOS JUNIO 2025</t>
+          <t>ASIENTO DE SUELDOS AGOSTO 25</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>30/06/2025</t>
+          <t>31/08/2025</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2024,33 +1968,33 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Bsas Sueldos</t>
+          <t>Bsas Cargas Sociales</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>44688838.55</v>
+        <v>19701.98</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>42101029</t>
+          <t>42101009</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>-44688838.55</v>
+        <v>-19701.98</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUELDOS MAYO </t>
+          <t>ASTO RECLASIF Y CONC DE CTAS</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>31/05/2025</t>
+          <t>30/06/2025</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2070,33 +2014,33 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Bsas Sueldos</t>
+          <t>Bsas Cargas Sociales</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>31952047.18</v>
+        <v>6538467.88</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>42101029</t>
+          <t>42102005</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>-31952047.18</v>
+        <v>-6538467.88</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>ASTO SUELDOS MARZO 2025</t>
+          <t>ASIENTO DE SUELDOS NOVIEMBRE 25</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>31/03/2025</t>
+          <t>30/11/2025</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2116,33 +2060,33 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Bsas Sueldos</t>
+          <t>Bsas Cargas Sociales</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>9389750.23</v>
+        <v>7877088.65</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>42102023</t>
+          <t>42101009</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>-9389750.23</v>
+        <v>-7877088.65</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Prov Agosto 25</t>
+          <t>ASIENTO DE SUELDOS NOVIEMBRE 25</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>31/08/2025</t>
+          <t>30/11/2025</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2162,33 +2106,33 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Bsas Sueldos</t>
+          <t>Bsas Cargas Sociales</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>8768547.869999999</v>
+        <v>2613068.89</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>42102023</t>
+          <t>42102005</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>-8768547.869999999</v>
+        <v>-2613068.89</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>ASIENTO SUELDOS FEBRERO 2025</t>
+          <t>Prov Agosto 25</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>31/08/2025</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2208,33 +2152,33 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Bsas Sueldos</t>
+          <t>Bsas Cargas Sociales</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>35735084.31</v>
+        <v>3026330.99</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>42101029</t>
+          <t>42102005</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>-35735084.31</v>
+        <v>-3026330.99</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>ASIENTO SUELDOS FEBRERO 2025</t>
+          <t>AJ X INFL NOVIEMBRE 25 CTAS DE RESULTADO</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>30/11/2025</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2254,33 +2198,33 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Bsas Sueldos</t>
+          <t>Bsas Cargas Sociales</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>9206174.59</v>
+        <v>11884681.73</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>42102023</t>
+          <t>42101009</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>-9206174.59</v>
+        <v>-11884681.73</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>ASIENTO SUELDOS ENERO 2025</t>
+          <t>REVERSION PROVISIONES</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>31/01/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2300,33 +2244,33 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Bsas Sueldos</t>
+          <t>Bsas Cargas Sociales</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>8555359.17</v>
+        <v>2613068.89</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>42102023</t>
+          <t>42102005</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>-8555359.17</v>
+        <v>-2613068.89</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ASTO SUELDOS MARZO 2025</t>
+          <t>REVERSION PROVISIONES</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>31/03/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2346,33 +2290,33 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Bsas Sueldos</t>
+          <t>Bsas Cargas Sociales</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>34536612.77</v>
+        <v>4153633.35</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>42101029</t>
+          <t>42102005</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>-34536612.77</v>
+        <v>-4153633.35</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>ASIENTO SUELDOS ENERO 2025</t>
+          <t>ASIENTO SUELDOS JULIO 25</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>31/01/2025</t>
+          <t>31/07/2025</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2387,7 +2331,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2397,19 +2341,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Pat Cargas Sociales</t>
+          <t>Bsas Cargas Sociales</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>17222285.97</v>
+        <v>10116157.5</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>42201009</t>
+          <t>42101009</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>-17222285.97</v>
+        <v>-10116157.5</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2433,38 +2377,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Pat Cargas Sociales</t>
+          <t>Bsas Cargas Sociales</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>15420875.54</v>
+        <v>11449872.27</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>42201009</t>
+          <t>42101009</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>-15420875.54</v>
+        <v>-11449872.27</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>ASTO SUELDOS MARZO 2025</t>
+          <t>ASIENTO SUELDOS JULIO 25</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>31/03/2025</t>
+          <t>31/07/2025</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2479,38 +2423,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Pat Cargas Sociales</t>
+          <t>Bsas Cargas Sociales</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>15316765.46</v>
+        <v>14249476.71</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>42201009</t>
+          <t>42101009</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>-15316765.46</v>
+        <v>-14249476.71</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUELDOS MAYO </t>
+          <t>AJ X INFL NOVIEMBRE 25 CTAS DE RESULTADO</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>31/05/2025</t>
+          <t>30/11/2025</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2525,38 +2469,38 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Pat Cargas Sociales</t>
+          <t>Bsas Sueldos</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>15475764.31</v>
+        <v>8834638.699999999</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>42201009</t>
+          <t>42102023</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>-15475764.31</v>
+        <v>-8834638.699999999</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>ASIENTO SUELDOS JULIO 25</t>
+          <t>ASTO SUELDOS ABRIL 2025</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>31/07/2025</t>
+          <t>30/04/2025</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2571,38 +2515,38 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Pat Cargas Sociales</t>
+          <t>Bsas Sueldos</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>15652866.82</v>
+        <v>43293151.23</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>42201009</t>
+          <t>42101029</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>-15652866.82</v>
+        <v>-43293151.23</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>SUELDOS JUNIO 2025</t>
+          <t>ASIENTO DE SUELDOS SEPTIEMBRE</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>30/06/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2617,38 +2561,38 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Pat Cargas Sociales</t>
+          <t>Bsas Sueldos</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>16138452.01</v>
+        <v>9389750.23</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>42201009</t>
+          <t>42102023</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>-16138452.01</v>
+        <v>-9389750.23</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>ASIENTO SUELDOS FEBRERO 2025</t>
+          <t>Prov Agosto 25</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>31/08/2025</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2663,38 +2607,38 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Pat Cargas Sociales</t>
+          <t>Bsas Sueldos</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>13771576.17</v>
+        <v>13413532.38</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>42201009</t>
+          <t>42102023</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>-13771576.17</v>
+        <v>-13413532.38</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Prov Agosto 25</t>
+          <t>SUELDOS JUNIO 2025</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>31/08/2025</t>
+          <t>30/06/2025</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2709,38 +2653,38 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Pat Cargas Sociales</t>
+          <t>Bsas Sueldos</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>14868817.45</v>
+        <v>16822069.17</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>42201009</t>
+          <t>42102023</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>-14868817.45</v>
+        <v>-16822069.17</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>ASIENTO SUELDOS ENERO 2025</t>
+          <t>ASIENTO SUELDOS JULIO 25</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>31/01/2025</t>
+          <t>31/07/2025</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2755,38 +2699,38 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Pat Sueldos</t>
+          <t>Bsas Sueldos</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>57723703.81</v>
+        <v>143074383.93</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>42201029</t>
+          <t>42101029</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>-57723703.81</v>
+        <v>-143074383.93</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Prov Agosto 25</t>
+          <t>SUELDOS JUNIO 2025</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>31/08/2025</t>
+          <t>30/06/2025</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -2801,7 +2745,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2811,19 +2755,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Pat Sueldos</t>
+          <t>Bsas Sueldos</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>59306538.01</v>
+        <v>43537788.49</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>42201029</t>
+          <t>42101029</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>-59306538.01</v>
+        <v>-43537788.49</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2847,38 +2791,38 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Pat Sueldos</t>
+          <t>Bsas Sueldos</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>58118409.78</v>
+        <v>40195172.43</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>42201029</t>
+          <t>42101029</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>-58118409.78</v>
+        <v>-40195172.43</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>ASIENTO SUELDOS ENERO 2025</t>
+          <t>ASIENTO DE SUELDOS AGOSTO 25</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>31/01/2025</t>
+          <t>31/08/2025</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -2893,38 +2837,38 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Pat Sueldos</t>
+          <t>Bsas Sueldos</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>68440770.40000001</v>
+        <v>9389750.23</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>42201029</t>
+          <t>42102023</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>-68440770.40000001</v>
+        <v>-9389750.23</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>ASIENTO SUELDOS FEBRERO 2025</t>
+          <t>ASIENTO DE SUELDOS AGOSTO 25</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>31/08/2025</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -2939,7 +2883,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2949,19 +2893,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Pat Sueldos</t>
+          <t>Bsas Sueldos</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53773581.3</v>
+        <v>9272920.189999999</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>42201029</t>
+          <t>42102023</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>-53773581.3</v>
+        <v>-9272920.189999999</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2985,38 +2929,38 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Pat Sueldos</t>
+          <t>Bsas Sueldos</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>57654206.87</v>
+        <v>44688838.55</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>42201029</t>
+          <t>42101029</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>-57654206.87</v>
+        <v>-44688838.55</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>ASTO SUELDOS MARZO 2025</t>
+          <t xml:space="preserve">SUELDOS MAYO </t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>31/03/2025</t>
+          <t>31/05/2025</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3031,38 +2975,38 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Pat Sueldos</t>
+          <t>Bsas Sueldos</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>62475446.2</v>
+        <v>8555359.17</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>42201029</t>
+          <t>42102023</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>-62475446.2</v>
+        <v>-8555359.17</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>ASTO SUELDOS ABRIL 2025</t>
+          <t>ASTO SUELDOS MARZO 2025</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>30/04/2025</t>
+          <t>31/03/2025</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3077,38 +3021,38 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Pat Sueldos</t>
+          <t>Bsas Sueldos</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>80243928.62</v>
+        <v>12903171.05</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>42201029</t>
+          <t>42102023</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>-80243928.62</v>
+        <v>-12903171.05</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>SUELDOS JUNIO 2025</t>
+          <t>AJ X INFL NOVIEMBRE 25 CTAS DE RESULTADO</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>30/06/2025</t>
+          <t>30/11/2025</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3128,30 +3072,38 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Ventas netas - Buenos Aires</t>
+          <t>Bsas Sueldos</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>121054196.105</v>
+        <v>60582773.59</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">     </t>
+          <t>42101029</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>121054196.105</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
+        <v>-60582773.59</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>AJ X INFL NOVIEMBRE 25 CTAS DE RESULTADO</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>30/11/2025</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>1.VENTAS</t>
+          <t>PERSONAL</t>
         </is>
       </c>
     </row>
@@ -3166,30 +3118,38 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Ventas netas - Buenos Aires</t>
+          <t>Bsas Sueldos</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>119115992.905</v>
+        <v>9389750.23</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">     </t>
+          <t>42102023</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>119115992.905</v>
-      </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
+        <v>-9389750.23</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>REVERSION PROVISIONES</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>01/09/2025</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>1.VENTAS</t>
+          <t>PERSONAL</t>
         </is>
       </c>
     </row>
@@ -3204,30 +3164,38 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Ventas netas - Buenos Aires</t>
+          <t>Bsas Sueldos</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>105233762.4225</v>
+        <v>40195172.43</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">     </t>
+          <t>42101029</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>105233762.4225</v>
-      </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
+        <v>-40195172.43</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>REVERSION PROVISIONES</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>01/09/2025</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>1.VENTAS</t>
+          <t>PERSONAL</t>
         </is>
       </c>
     </row>
@@ -3242,30 +3210,38 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Ventas netas - Buenos Aires</t>
+          <t>Bsas Sueldos</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>38447277.54</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">     </t>
+          <t>42102023</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
+        <v>-38447277.54</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>ASIENTO DE SUELDOS NOVIEMBRE 25</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>30/11/2025</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>1.VENTAS</t>
+          <t>PERSONAL</t>
         </is>
       </c>
     </row>
@@ -3280,30 +3256,38 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Ventas netas - Buenos Aires</t>
+          <t>Bsas Sueldos</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221028761.82</v>
+        <v>45222116.99</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">     </t>
+          <t>42101029</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>221028761.82</v>
-      </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
+        <v>-45222116.99</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>ASIENTO DE SUELDOS NOVIEMBRE 25</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>30/11/2025</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>1.VENTAS</t>
+          <t>PERSONAL</t>
         </is>
       </c>
     </row>
@@ -3318,30 +3302,38 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Ventas netas - Buenos Aires</t>
+          <t>Bsas Sueldos</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>134570910.355</v>
+        <v>38826779.14</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">     </t>
+          <t>42101029</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>134570910.355</v>
-      </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
+        <v>-38826779.14</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>ASTO SUELDOS ABRIL 2025</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>30/04/2025</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>1.VENTAS</t>
+          <t>PERSONAL</t>
         </is>
       </c>
     </row>
@@ -3356,30 +3348,38 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Ventas netas - Buenos Aires</t>
+          <t>Bsas Sueldos</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>157836181.625</v>
+        <v>34536612.77</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">     </t>
+          <t>42101029</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>157836181.625</v>
-      </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
+        <v>-34536612.77</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>ASIENTO SUELDOS ENERO 2025</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>31/01/2025</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>1.VENTAS</t>
+          <t>PERSONAL</t>
         </is>
       </c>
     </row>
@@ -3394,30 +3394,38 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Ventas netas - Buenos Aires</t>
+          <t>Bsas Sueldos</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>113505158.73</v>
+        <v>40195172.43</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">     </t>
+          <t>42101029</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>113505158.73</v>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
+        <v>-40195172.43</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Prov Agosto 25</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>31/08/2025</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>1.VENTAS</t>
+          <t>PERSONAL</t>
         </is>
       </c>
     </row>
@@ -3432,30 +3440,38 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Ventas netas - Buenos Aires</t>
+          <t>Bsas Sueldos</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100449899.183</v>
+        <v>9206174.59</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">     </t>
+          <t>42102023</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>100449899.183</v>
-      </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
+        <v>-9206174.59</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>ASIENTO SUELDOS ENERO 2025</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>31/01/2025</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>1.VENTAS</t>
+          <t>PERSONAL</t>
         </is>
       </c>
     </row>
@@ -3470,28 +3486,2208 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Bsas Sueldos</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>47224204.38</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>42101029</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>-47224204.38</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>ASIENTO DE SUELDOS OCTUBRE 25</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Bsas Sueldos</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>35735084.31</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>42101029</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>-35735084.31</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>ASIENTO SUELDOS FEBRERO 2025</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>28/02/2025</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Bsas Sueldos</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>8768547.869999999</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>42102023</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>-8768547.869999999</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>ASIENTO SUELDOS FEBRERO 2025</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>28/02/2025</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Bsas Sueldos</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>9916457.060000001</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>42102023</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>-9916457.060000001</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>ASIENTO DE SUELDOS SEPTIEMBRE</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Bsas Sueldos</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>31952047.18</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>42101029</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>-31952047.18</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>ASTO SUELDOS MARZO 2025</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>31/03/2025</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Bsas Sueldos</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>10893642.44</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>42102023</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>-10893642.44</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>ASIENTO DE SUELDOS OCTUBRE 25</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Pat Cargas Sociales</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>16730355.42</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>42201009</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>-16730355.42</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>ASIENTO DE SUELDOS AGOSTO 25</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>31/08/2025</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Pat Cargas Sociales</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>13771576.17</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>42201009</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>-13771576.17</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>REVERSION PROVISIONES</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>01/09/2025</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Pat Cargas Sociales</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>16379884.23</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>42201009</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>-16379884.23</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>ASIENTO DE SUELDOS OCTUBRE 25</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Pat Cargas Sociales</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>2334829.8</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>42201009</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>-2334829.8</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>ASTO DE AJ Y RECLASIF DE CUENTAS</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>30/11/2025</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Pat Cargas Sociales</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>17266481.82</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>42201009</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>-17266481.82</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>ASIENTO DE SUELDOS SEPTIEMBRE</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Pat Cargas Sociales</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>16989266.07</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>42201009</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>-16989266.07</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>ASIENTO DE SUELDOS NOVIEMBRE 25</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>30/11/2025</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Pat Cargas Sociales</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>20420594.3</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>42201009</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>-20420594.3</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>AJ X INFL NOVIEMBRE 25 CTAS DE RESULTADO</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>30/11/2025</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Pat Cargas Sociales</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>13771576.17</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>42201009</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>-13771576.17</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Prov Agosto 25</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>31/08/2025</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Pat Cargas Sociales</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>16138452.01</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>42201009</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>-16138452.01</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>ASIENTO SUELDOS FEBRERO 2025</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>28/02/2025</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Pat Cargas Sociales</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>15420875.54</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>42201009</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>-15420875.54</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>ASTO SUELDOS MARZO 2025</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>31/03/2025</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Pat Cargas Sociales</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>17222285.97</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>42201009</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>-17222285.97</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>ASTO SUELDOS ABRIL 2025</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>30/04/2025</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Pat Cargas Sociales</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>15316765.46</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>42201009</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>-15316765.46</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUELDOS MAYO </t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>31/05/2025</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Pat Cargas Sociales</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>14868817.45</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>42201009</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>-14868817.45</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>ASIENTO SUELDOS ENERO 2025</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>31/01/2025</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Pat Cargas Sociales</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>15652866.82</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>42201009</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>-15652866.82</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>SUELDOS JUNIO 2025</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>30/06/2025</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Pat Cargas Sociales</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>15475764.31</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>42201009</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>-15475764.31</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>ASIENTO SUELDOS JULIO 25</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>31/07/2025</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Pat Sueldos</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>80155404.63</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>42201029</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>-80155404.63</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>AJ X INFL NOVIEMBRE 25 CTAS DE RESULTADO</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>30/11/2025</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Pat Sueldos</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>57723703.81</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>42201029</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>-57723703.81</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>REVERSION PROVISIONES</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>01/09/2025</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Pat Sueldos</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>80243928.62</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>42201029</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>-80243928.62</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>SUELDOS JUNIO 2025</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>30/06/2025</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Pat Sueldos</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>99122852.52</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>42201029</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>-99122852.52</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>ASIENTO DE SUELDOS NOVIEMBRE 25</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>30/11/2025</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Pat Sueldos</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>57723703.81</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>42201029</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>-57723703.81</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Prov Agosto 25</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>31/08/2025</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Pat Sueldos</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>59306538.01</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>42201029</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>-59306538.01</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>ASIENTO SUELDOS JULIO 25</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>31/07/2025</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Pat Sueldos</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>68440770.40000001</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>42201029</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>-68440770.40000001</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>ASIENTO SUELDOS FEBRERO 2025</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>28/02/2025</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Pat Sueldos</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>58118409.78</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>42201029</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>-58118409.78</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>ASIENTO SUELDOS ENERO 2025</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>31/01/2025</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Pat Sueldos</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>57723704.81</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>42201029</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>-57723704.81</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>ASIENTO DE SUELDOS AGOSTO 25</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>31/08/2025</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Pat Sueldos</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>57654206.87</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>42201029</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>-57654206.87</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>ASTO SUELDOS MARZO 2025</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>31/03/2025</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Pat Sueldos</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>62475446.2</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>42201029</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>-62475446.2</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>ASTO SUELDOS ABRIL 2025</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>30/04/2025</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Pat Sueldos</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>59635458.61</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>42201029</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>-59635458.61</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>ASIENTO DE SUELDOS SEPTIEMBRE</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Pat Sueldos</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>53773581.3</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>42201029</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>-53773581.3</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUELDOS MAYO </t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>31/05/2025</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Pat Sueldos</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>61589623.5</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>42201029</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>-61589623.5</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>ASIENTO DE SUELDOS OCTUBRE 25</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
         <is>
           <t>Ventas netas - Buenos Aires</t>
         </is>
       </c>
-      <c r="E70" t="n">
+      <c r="E105" t="n">
+        <v>134570910.355</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     </t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>134570910.355</v>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>1.VENTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Ventas netas - Buenos Aires</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>121054196.105</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     </t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>121054196.105</v>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>1.VENTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Ventas netas - Buenos Aires</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>119115992.905</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     </t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>119115992.905</v>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>1.VENTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Ventas netas - Buenos Aires</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>105233762.4225</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     </t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>105233762.4225</v>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>1.VENTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Ventas netas - Buenos Aires</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>100449899.183</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     </t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>100449899.183</v>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>1.VENTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Ventas netas - Buenos Aires</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>221028761.82</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     </t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>221028761.82</v>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>1.VENTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Ventas netas - Buenos Aires</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>157836181.625</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     </t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>157836181.625</v>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>1.VENTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Ventas netas - Buenos Aires</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>174897636.495</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     </t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>174897636.495</v>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>1.VENTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Ventas netas - Buenos Aires</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>151214301.645</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     </t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>151214301.645</v>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>1.VENTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Ventas netas - Buenos Aires</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>158653636.82</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     </t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>158653636.82</v>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>1.VENTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Ventas netas - Buenos Aires</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>158890904.0784</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     </t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>158890904.0784</v>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>1.VENTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Ventas netas - Buenos Aires</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>167719930.635</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     </t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>167719930.635</v>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>1.VENTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Ventas netas - Buenos Aires</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>159578990.165</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     </t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>159578990.165</v>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>1.VENTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Ventas netas - Buenos Aires</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>171230406.595</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     </t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>171230406.595</v>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>1.VENTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Ventas netas - Buenos Aires</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>155328133.6</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     </t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>155328133.6</v>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>1.VENTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Ventas netas - Buenos Aires</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
         <v>131554945.435</v>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F120" t="inlineStr">
         <is>
           <t xml:space="preserve">     </t>
         </is>
       </c>
-      <c r="G70" t="n">
+      <c r="G120" t="n">
         <v>131554945.435</v>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr">
         <is>
           <t>1.VENTAS</t>
         </is>
